--- a/tinker lab ca 1.xlsx
+++ b/tinker lab ca 1.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>Sr</t>
   </si>
@@ -99,6 +99,18 @@
   </si>
   <si>
     <t>emp15</t>
+  </si>
+  <si>
+    <t>da</t>
+  </si>
+  <si>
+    <t>ta</t>
+  </si>
+  <si>
+    <t>hra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pf </t>
   </si>
 </sst>
 </file>
@@ -156,7 +168,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -179,6 +191,7 @@
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -459,7 +472,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J16"/>
+  <dimension ref="A2:J22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
@@ -467,515 +480,559 @@
     <col min="10" max="10" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="8">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B7" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J7" s="1" t="s">
         <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="3">
-        <v>2000</v>
-      </c>
-      <c r="D2" s="4">
-        <v>1500</v>
-      </c>
-      <c r="E2" s="3">
-        <v>300</v>
-      </c>
-      <c r="F2" s="3">
-        <v>300</v>
-      </c>
-      <c r="G2" s="3">
-        <v>500</v>
-      </c>
-      <c r="H2" s="4">
-        <v>4100</v>
-      </c>
-      <c r="I2" s="3">
-        <v>500</v>
-      </c>
-      <c r="J2" s="4">
-        <v>3600</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="3">
-        <v>5000</v>
-      </c>
-      <c r="D3" s="4">
-        <v>3750</v>
-      </c>
-      <c r="E3" s="3">
-        <v>750</v>
-      </c>
-      <c r="F3" s="3">
-        <v>750</v>
-      </c>
-      <c r="G3" s="4">
-        <v>1250</v>
-      </c>
-      <c r="H3" s="4">
-        <v>10250</v>
-      </c>
-      <c r="I3" s="4">
-        <v>1250</v>
-      </c>
-      <c r="J3" s="4">
-        <v>9000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="3">
-        <v>18000</v>
-      </c>
-      <c r="D4" s="4">
-        <v>13500</v>
-      </c>
-      <c r="E4" s="4">
-        <v>2700</v>
-      </c>
-      <c r="F4" s="4">
-        <v>2700</v>
-      </c>
-      <c r="G4" s="4">
-        <v>4500</v>
-      </c>
-      <c r="H4" s="4">
-        <v>36900</v>
-      </c>
-      <c r="I4" s="4">
-        <v>4500</v>
-      </c>
-      <c r="J4" s="4">
-        <v>32000</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="3">
-        <v>2233</v>
-      </c>
-      <c r="D5" s="4">
-        <v>1674.75</v>
-      </c>
-      <c r="E5" s="3">
-        <v>334.95</v>
-      </c>
-      <c r="F5" s="3">
-        <v>334.95</v>
-      </c>
-      <c r="G5" s="3">
-        <v>558.25</v>
-      </c>
-      <c r="H5" s="4">
-        <v>4577.6499999999996</v>
-      </c>
-      <c r="I5" s="3">
-        <v>558.25</v>
-      </c>
-      <c r="J5" s="4">
-        <v>4019.4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="3">
-        <v>14556</v>
-      </c>
-      <c r="D6" s="4">
-        <v>10917</v>
-      </c>
-      <c r="E6" s="4">
-        <v>2183.4</v>
-      </c>
-      <c r="F6" s="4">
-        <v>2183.4</v>
-      </c>
-      <c r="G6" s="4">
-        <v>3639</v>
-      </c>
-      <c r="H6" s="4">
-        <v>29839.8</v>
-      </c>
-      <c r="I6" s="4">
-        <v>3639</v>
-      </c>
-      <c r="J6" s="4">
-        <v>26200.799999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="3">
-        <v>6778</v>
-      </c>
-      <c r="D7" s="4">
-        <v>5083.5</v>
-      </c>
-      <c r="E7" s="4">
-        <v>1016.7</v>
-      </c>
-      <c r="F7" s="4">
-        <v>1016.7</v>
-      </c>
-      <c r="G7" s="4">
-        <v>1694.5</v>
-      </c>
-      <c r="H7" s="4">
-        <v>13894.9</v>
-      </c>
-      <c r="I7" s="4">
-        <v>1694.5</v>
-      </c>
-      <c r="J7" s="4">
-        <v>12200.4</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C8" s="3">
-        <v>9667</v>
+        <v>2000</v>
       </c>
       <c r="D8" s="4">
-        <v>7250.25</v>
-      </c>
-      <c r="E8" s="4">
-        <v>1450.05</v>
-      </c>
-      <c r="F8" s="4">
-        <v>1450.05</v>
-      </c>
-      <c r="G8" s="4">
-        <v>2416.75</v>
+        <v>1500</v>
+      </c>
+      <c r="E8" s="3">
+        <v>300</v>
+      </c>
+      <c r="F8" s="3">
+        <v>300</v>
+      </c>
+      <c r="G8" s="3">
+        <v>500</v>
       </c>
       <c r="H8" s="4">
-        <v>19817.349999999999</v>
-      </c>
-      <c r="I8" s="4">
-        <v>2416.75</v>
+        <v>4100</v>
+      </c>
+      <c r="I8" s="3">
+        <v>500</v>
       </c>
       <c r="J8" s="4">
-        <v>17400.599999999999</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C9" s="3">
-        <v>12365</v>
+        <v>5000</v>
       </c>
       <c r="D9" s="4">
-        <v>9273.75</v>
-      </c>
-      <c r="E9" s="4">
-        <v>1854.75</v>
-      </c>
-      <c r="F9" s="4">
-        <v>1854.75</v>
+        <v>3750</v>
+      </c>
+      <c r="E9" s="3">
+        <v>750</v>
+      </c>
+      <c r="F9" s="3">
+        <v>750</v>
       </c>
       <c r="G9" s="4">
-        <v>3091.25</v>
+        <v>1250</v>
       </c>
       <c r="H9" s="4">
-        <v>25348.25</v>
+        <v>10250</v>
       </c>
       <c r="I9" s="4">
-        <v>3091.25</v>
+        <v>1250</v>
       </c>
       <c r="J9" s="4">
-        <v>22257</v>
+        <v>9000</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C10" s="3">
-        <v>7987</v>
+        <v>18000</v>
       </c>
       <c r="D10" s="4">
-        <v>5990.25</v>
+        <v>13500</v>
       </c>
       <c r="E10" s="4">
-        <v>1198.05</v>
+        <v>2700</v>
       </c>
       <c r="F10" s="4">
-        <v>1198.05</v>
+        <v>2700</v>
       </c>
       <c r="G10" s="4">
-        <v>1996.75</v>
+        <v>4500</v>
       </c>
       <c r="H10" s="4">
-        <v>16373.35</v>
+        <v>36900</v>
       </c>
       <c r="I10" s="4">
-        <v>1996.75</v>
+        <v>4500</v>
       </c>
       <c r="J10" s="4">
-        <v>14376.6</v>
+        <v>32000</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C11" s="3">
-        <v>9856</v>
+        <v>2233</v>
       </c>
       <c r="D11" s="4">
-        <v>7392</v>
-      </c>
-      <c r="E11" s="4">
-        <v>1478.4</v>
-      </c>
-      <c r="F11" s="4">
-        <v>1478.4</v>
-      </c>
-      <c r="G11" s="4">
-        <v>2464</v>
+        <v>1674.75</v>
+      </c>
+      <c r="E11" s="3">
+        <v>334.95</v>
+      </c>
+      <c r="F11" s="3">
+        <v>334.95</v>
+      </c>
+      <c r="G11" s="3">
+        <v>558.25</v>
       </c>
       <c r="H11" s="4">
-        <v>20204.8</v>
-      </c>
-      <c r="I11" s="4">
-        <v>2464</v>
+        <v>4577.6499999999996</v>
+      </c>
+      <c r="I11" s="3">
+        <v>558.25</v>
       </c>
       <c r="J11" s="4">
-        <v>17740.8</v>
+        <v>4019.4</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C12" s="3">
-        <v>8776</v>
+        <v>14556</v>
       </c>
       <c r="D12" s="4">
-        <v>6582</v>
+        <v>10917</v>
       </c>
       <c r="E12" s="4">
-        <v>1316.4</v>
+        <v>2183.4</v>
       </c>
       <c r="F12" s="4">
-        <v>1316.4</v>
+        <v>2183.4</v>
       </c>
       <c r="G12" s="4">
-        <v>2194</v>
+        <v>3639</v>
       </c>
       <c r="H12" s="4">
-        <v>17990.8</v>
+        <v>29839.8</v>
       </c>
       <c r="I12" s="4">
-        <v>2194</v>
+        <v>3639</v>
       </c>
       <c r="J12" s="4">
-        <v>15796.8</v>
+        <v>26200.799999999999</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C13" s="3">
-        <v>12454</v>
+        <v>6778</v>
       </c>
       <c r="D13" s="4">
-        <v>9340.5</v>
+        <v>5083.5</v>
       </c>
       <c r="E13" s="4">
-        <v>1868.1</v>
+        <v>1016.7</v>
       </c>
       <c r="F13" s="4">
-        <v>1868.1</v>
+        <v>1016.7</v>
       </c>
       <c r="G13" s="4">
-        <v>3113.5</v>
+        <v>1694.5</v>
       </c>
       <c r="H13" s="4">
-        <v>25530.7</v>
+        <v>13894.9</v>
       </c>
       <c r="I13" s="4">
-        <v>3113.5</v>
+        <v>1694.5</v>
       </c>
       <c r="J13" s="4">
-        <v>22417.200000000001</v>
+        <v>12200.4</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C14" s="3">
-        <v>4564</v>
+        <v>9667</v>
       </c>
       <c r="D14" s="4">
-        <v>3423</v>
-      </c>
-      <c r="E14" s="3">
-        <v>684.6</v>
-      </c>
-      <c r="F14" s="3">
-        <v>684.6</v>
+        <v>7250.25</v>
+      </c>
+      <c r="E14" s="4">
+        <v>1450.05</v>
+      </c>
+      <c r="F14" s="4">
+        <v>1450.05</v>
       </c>
       <c r="G14" s="4">
-        <v>1141</v>
+        <v>2416.75</v>
       </c>
       <c r="H14" s="4">
-        <v>9356.2000000000007</v>
+        <v>19817.349999999999</v>
       </c>
       <c r="I14" s="4">
-        <v>1141</v>
+        <v>2416.75</v>
       </c>
       <c r="J14" s="4">
-        <v>8215.2000000000007</v>
+        <v>17400.599999999999</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
+        <v>8</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="3">
+        <v>12365</v>
+      </c>
+      <c r="D15" s="4">
+        <v>9273.75</v>
+      </c>
+      <c r="E15" s="4">
+        <v>1854.75</v>
+      </c>
+      <c r="F15" s="4">
+        <v>1854.75</v>
+      </c>
+      <c r="G15" s="4">
+        <v>3091.25</v>
+      </c>
+      <c r="H15" s="4">
+        <v>25348.25</v>
+      </c>
+      <c r="I15" s="4">
+        <v>3091.25</v>
+      </c>
+      <c r="J15" s="4">
+        <v>22257</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="2">
+        <v>9</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="3">
+        <v>7987</v>
+      </c>
+      <c r="D16" s="4">
+        <v>5990.25</v>
+      </c>
+      <c r="E16" s="4">
+        <v>1198.05</v>
+      </c>
+      <c r="F16" s="4">
+        <v>1198.05</v>
+      </c>
+      <c r="G16" s="4">
+        <v>1996.75</v>
+      </c>
+      <c r="H16" s="4">
+        <v>16373.35</v>
+      </c>
+      <c r="I16" s="4">
+        <v>1996.75</v>
+      </c>
+      <c r="J16" s="4">
+        <v>14376.6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="2">
+        <v>10</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="3">
+        <v>9856</v>
+      </c>
+      <c r="D17" s="4">
+        <v>7392</v>
+      </c>
+      <c r="E17" s="4">
+        <v>1478.4</v>
+      </c>
+      <c r="F17" s="4">
+        <v>1478.4</v>
+      </c>
+      <c r="G17" s="4">
+        <v>2464</v>
+      </c>
+      <c r="H17" s="4">
+        <v>20204.8</v>
+      </c>
+      <c r="I17" s="4">
+        <v>2464</v>
+      </c>
+      <c r="J17" s="4">
+        <v>17740.8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="2">
+        <v>11</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C18" s="3">
+        <v>8776</v>
+      </c>
+      <c r="D18" s="4">
+        <v>6582</v>
+      </c>
+      <c r="E18" s="4">
+        <v>1316.4</v>
+      </c>
+      <c r="F18" s="4">
+        <v>1316.4</v>
+      </c>
+      <c r="G18" s="4">
+        <v>2194</v>
+      </c>
+      <c r="H18" s="4">
+        <v>17990.8</v>
+      </c>
+      <c r="I18" s="4">
+        <v>2194</v>
+      </c>
+      <c r="J18" s="4">
+        <v>15796.8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="2">
+        <v>12</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="3">
+        <v>12454</v>
+      </c>
+      <c r="D19" s="4">
+        <v>9340.5</v>
+      </c>
+      <c r="E19" s="4">
+        <v>1868.1</v>
+      </c>
+      <c r="F19" s="4">
+        <v>1868.1</v>
+      </c>
+      <c r="G19" s="4">
+        <v>3113.5</v>
+      </c>
+      <c r="H19" s="4">
+        <v>25530.7</v>
+      </c>
+      <c r="I19" s="4">
+        <v>3113.5</v>
+      </c>
+      <c r="J19" s="4">
+        <v>22417.200000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="2">
+        <v>13</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="3">
+        <v>4564</v>
+      </c>
+      <c r="D20" s="4">
+        <v>3423</v>
+      </c>
+      <c r="E20" s="3">
+        <v>684.6</v>
+      </c>
+      <c r="F20" s="3">
+        <v>684.6</v>
+      </c>
+      <c r="G20" s="4">
+        <v>1141</v>
+      </c>
+      <c r="H20" s="4">
+        <v>9356.2000000000007</v>
+      </c>
+      <c r="I20" s="4">
+        <v>1141</v>
+      </c>
+      <c r="J20" s="4">
+        <v>8215.2000000000007</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2">
         <v>14</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B21" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C21" s="3">
         <v>8678</v>
       </c>
-      <c r="D15" s="4">
+      <c r="D21" s="4">
         <v>6508.5</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E21" s="4">
         <v>1301.7</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F21" s="4">
         <v>1301.7</v>
       </c>
-      <c r="G15" s="4">
+      <c r="G21" s="4">
         <v>2169.5</v>
       </c>
-      <c r="H15" s="4">
+      <c r="H21" s="4">
         <v>17789.900000000001</v>
       </c>
-      <c r="I15" s="4">
+      <c r="I21" s="4">
         <v>2169.5</v>
       </c>
-      <c r="J15" s="4">
+      <c r="J21" s="4">
         <v>15620.4</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="5">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="5">
         <v>15</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B22" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C22" s="6">
         <v>25000</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D22" s="7">
         <v>18750</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E22" s="7">
         <v>3750</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F22" s="7">
         <v>3750</v>
       </c>
-      <c r="G16" s="7">
+      <c r="G22" s="7">
         <v>6250</v>
       </c>
-      <c r="H16" s="7">
+      <c r="H22" s="7">
         <v>51250</v>
       </c>
-      <c r="I16" s="7">
+      <c r="I22" s="7">
         <v>6250</v>
       </c>
-      <c r="J16" s="7">
+      <c r="J22" s="7">
         <v>45000</v>
       </c>
     </row>
